--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.94181265106022</v>
+        <v>4.865544555797286</v>
       </c>
       <c r="D2" t="n">
-        <v>29.51190672504176</v>
+        <v>4.795684842819286</v>
       </c>
       <c r="E2" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F2" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.09885475607505</v>
+        <v>3.428563897862196</v>
       </c>
       <c r="D3" t="n">
-        <v>20.71559164347267</v>
+        <v>3.366283642064309</v>
       </c>
       <c r="E3" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F3" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.24954075298061</v>
+        <v>8.490550372359349</v>
       </c>
       <c r="D4" t="n">
-        <v>52.34314731964495</v>
+        <v>8.505761439442304</v>
       </c>
       <c r="E4" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F4" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.86829772671025</v>
+        <v>11.51609838059042</v>
       </c>
       <c r="D5" t="n">
-        <v>70.12769921366642</v>
+        <v>11.39575112222079</v>
       </c>
       <c r="E5" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F5" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.73665757787925</v>
+        <v>8.732206856405378</v>
       </c>
       <c r="D6" t="n">
-        <v>52.03003698338957</v>
+        <v>8.454881009800806</v>
       </c>
       <c r="E6" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F6" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.82103044616696</v>
+        <v>3.058417447502131</v>
       </c>
       <c r="D7" t="n">
-        <v>20.87722894236953</v>
+        <v>3.392549703135048</v>
       </c>
       <c r="E7" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F7" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.12010042573858</v>
+        <v>4.244516319182519</v>
       </c>
       <c r="D8" t="n">
-        <v>24.71082513690006</v>
+        <v>4.01550908474626</v>
       </c>
       <c r="E8" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F8" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.43541317474421</v>
+        <v>4.783254640895933</v>
       </c>
       <c r="D9" t="n">
-        <v>29.01275412023162</v>
+        <v>4.714572544537638</v>
       </c>
       <c r="E9" t="n">
-        <v>17.54830316909499</v>
+        <v>2.851599264977936</v>
       </c>
       <c r="F9" t="n">
-        <v>17.15149540423197</v>
+        <v>2.787118003187695</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
